--- a/Result/profitability/6754.xlsx
+++ b/Result/profitability/6754.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AM33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4494,6 +4494,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6754</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>792</v>
+      </c>
+      <c r="D33" t="n">
+        <v>613</v>
+      </c>
+      <c r="E33" t="n">
+        <v>179</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="G33" t="n">
+        <v>41</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5.13%</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>44</v>
+      </c>
+      <c r="K33" t="n">
+        <v>37</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8962499999999999</v>
+      </c>
+      <c r="N33" t="n">
+        <v>23.525</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>-0.2399999999999984</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-0.01049868766404194</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.06999999999999995</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.690000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.08074534161490687</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK33" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
